--- a/รายได้-UFA66-03-07-2022-03-13-2022&.xlsx
+++ b/รายได้-UFA66-03-07-2022-03-13-2022&.xlsx
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>-678</v>
+        <v>0</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>-678</v>
@@ -11691,7 +11691,7 @@
         <v>-500</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>-8154</v>
+        <v>0</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>-8154</v>
@@ -11743,7 +11743,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>-989</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>-526</v>
@@ -11769,7 +11769,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>-13321</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>-13151</v>
@@ -11795,7 +11795,7 @@
         <v>-4400</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>-39238</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>-39238</v>
@@ -11821,7 +11821,7 @@
         <v>-6</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>-4141</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>-3355</v>
@@ -11847,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>-1181</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>0</v>
@@ -11873,7 +11873,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>-2191</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>-2132</v>
@@ -11899,7 +11899,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>-1132</v>
+        <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>-1132</v>
@@ -11925,7 +11925,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>-267</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>-139</v>
@@ -11951,7 +11951,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>-388</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>-388</v>
@@ -11977,7 +11977,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>-978</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>-810</v>
@@ -12003,7 +12003,7 @@
         <v>-100</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>-1991</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>-1991</v>
@@ -12029,7 +12029,7 @@
         <v>-3200</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>-19856</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>-9433</v>
@@ -12055,7 +12055,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>-5494</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>-5133</v>
@@ -12081,7 +12081,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>-276</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>-276</v>
@@ -12107,7 +12107,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>-39538</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
         <v>-38827</v>
@@ -12159,7 +12159,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>-3875</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>-35</v>
@@ -12237,7 +12237,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>-19242</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>-963</v>
@@ -12263,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>-1025</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>-509</v>
@@ -12289,7 +12289,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>-3772</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
         <v>-3483</v>
@@ -12315,7 +12315,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
         <v>-60</v>
@@ -12341,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>-663</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
         <v>0</v>
@@ -12393,7 +12393,7 @@
         <v>-19</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>-6408</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0" t="n">
         <v>-1883</v>
@@ -12419,7 +12419,7 @@
         <v>-12</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>-17253</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>-12643</v>
@@ -12445,7 +12445,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>-867</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0" t="n">
         <v>-867</v>
@@ -12471,7 +12471,7 @@
         <v>-412</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>-10326</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0" t="n">
         <v>-5542</v>
@@ -12497,7 +12497,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>-2458</v>
+        <v>0</v>
       </c>
       <c r="E34" s="0" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>-5233</v>
+        <v>0</v>
       </c>
       <c r="E36" s="0" t="n">
         <v>-5174</v>
@@ -12601,7 +12601,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>-479</v>
@@ -12653,7 +12653,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>-10281</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0" t="n">
         <v>-4920</v>
@@ -12679,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>-120</v>
@@ -12705,7 +12705,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>-5129</v>
+        <v>0</v>
       </c>
       <c r="E42" s="0" t="n">
         <v>-3840</v>
@@ -12731,7 +12731,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>-871</v>
+        <v>0</v>
       </c>
       <c r="E43" s="0" t="n">
         <v>-871</v>
@@ -12757,7 +12757,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>-276</v>
+        <v>0</v>
       </c>
       <c r="E44" s="0" t="n">
         <v>-256</v>
@@ -12783,7 +12783,7 @@
         <v>-1313</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>-17134</v>
+        <v>0</v>
       </c>
       <c r="E45" s="0" t="n">
         <v>-8686</v>
@@ -12809,7 +12809,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>-1986</v>
+        <v>0</v>
       </c>
       <c r="E46" s="0" t="n">
         <v>-1240</v>
@@ -12835,7 +12835,7 @@
         <v>-12</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>-20507</v>
+        <v>0</v>
       </c>
       <c r="E47" s="0" t="n">
         <v>-20145</v>
@@ -12861,7 +12861,7 @@
         <v>-30</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>-7941</v>
+        <v>0</v>
       </c>
       <c r="E48" s="0" t="n">
         <v>-7363</v>
@@ -12887,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>-5642</v>
+        <v>0</v>
       </c>
       <c r="E49" s="0" t="n">
         <v>-5642</v>
@@ -12913,7 +12913,7 @@
         <v>-500</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>-47587</v>
+        <v>0</v>
       </c>
       <c r="E50" s="0" t="n">
         <v>-5465</v>
@@ -12939,7 +12939,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>-695</v>
+        <v>0</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>-375</v>
@@ -12965,7 +12965,7 @@
         <v>-9</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>-11128</v>
+        <v>0</v>
       </c>
       <c r="E52" s="0" t="n">
         <v>-10459</v>
@@ -12991,7 +12991,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>-3938</v>
+        <v>0</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>-3938</v>
@@ -13043,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>-8709</v>
+        <v>0</v>
       </c>
       <c r="E55" s="0" t="n">
         <v>-7228</v>
@@ -13069,7 +13069,7 @@
         <v>-2762</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>-44444</v>
+        <v>0</v>
       </c>
       <c r="E56" s="0" t="n">
         <v>-36287</v>
@@ -13095,7 +13095,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E57" s="0" t="n">
         <v>-24</v>
@@ -13147,7 +13147,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>-7797</v>
+        <v>0</v>
       </c>
       <c r="E59" s="0" t="n">
         <v>-7570</v>
